--- a/docs/dominio-metrico/migracion/cuestionarios/elisa-dido.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/elisa-dido.xlsx
@@ -21,25 +21,25 @@
     <t>Migración métrica · Elisa Dido</t>
   </si>
   <si>
-    <t>Para Blanca Ballester Morell · generado el 2026-09-19</t>
-  </si>
-  <si>
-    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, con este mismo texto. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
-  </si>
-  <si>
-    <t>En Responder están las preguntas que no hemos podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
-  </si>
-  <si>
-    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiremos a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
-  </si>
-  <si>
-    <t>En Confirmar aparecen las respuestas que hemos rellenado nosotros a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+    <t>Para Blanca Ballester Morell · generado el 2026-09-20</t>
+  </si>
+  <si>
+    <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
+  </si>
+  <si>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+  </si>
+  <si>
+    <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
+  </si>
+  <si>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
   </si>
   <si>
     <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
   </si>
   <si>
-    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntaselo a David antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y corregir allí lo que haga falta.</t>
+    <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
   </si>
   <si>
     <t>Cuando no hay desplegable, los formatos son estos:</t>

--- a/docs/dominio-metrico/migracion/cuestionarios/elisa-dido.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/elisa-dido.xlsx
@@ -33,10 +33,10 @@
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
   </si>
   <si>
-    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
-  </si>
-  <si>
-    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual. Si tienes a mano el número de sílabas de algún verso hipométrico o hipermétrico, ponlo en la columna «Sílabas»; si no, se registra simplemente que el verso tiene menos o más sílabas de las que le tocan, sin dar una cifra.</t>
+    <t>En Confirmar aparecen las respuestas que he rellenado yo a partir del término que elegiste en su día: la asonancia de un romance, el esquema de una octava real «regular», o que un endecasílabo suelto «puro» no lleva pareados. Ahí van también los tramos que vuelven a ser una sola secuencia. Solo hay que revisarlas. Si alguna no es así, elige «No es así» y escribe al lado lo que corresponde.</t>
+  </si>
+  <si>
+    <t>En Desviaciones están los versos hipométricos e hipermétricos, las rimas defectuosas y las lagunas que anotaste, con tus notas, y cómo quedan en el modelo nuevo. Se trasladan tal cual, así que basta con revisarlas: la columna «¿Correcto?» tiene el mismo desplegable que la pestaña anterior y solo hay que tocarla si algo no queda como digo. La columna «Sílabas del verso» es únicamente para los versos hipométricos e hipermétricos, por si tienes a mano cuántas sílabas mide el verso; si no la rellenas, se registra que tiene menos o más de las que le tocan, sin dar una cifra. En las demás filas esa celda está apagada.</t>
   </si>
   <si>
     <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
@@ -309,7 +309,7 @@
     <t>Cómo queda</t>
   </si>
   <si>
-    <t>Sílabas</t>
+    <t>Sílabas del verso</t>
   </si>
   <si>
     <t>#</t>
@@ -1857,7 +1857,7 @@
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
     <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>

--- a/docs/dominio-metrico/migracion/cuestionarios/elisa-dido.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/elisa-dido.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="138">
   <si>
     <t>Migración métrica · Elisa Dido</t>
   </si>
   <si>
-    <t>Para Blanca Ballester Morell · generado el 2026-09-20</t>
+    <t>Para Blanca Ballester Morell · generado el 2026-09-21</t>
   </si>
   <si>
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
@@ -111,66 +111,87 @@
     <t/>
   </si>
   <si>
+    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11») (son 48 versos)</t>
+  </si>
+  <si>
+    <t>R|7116f6e7-c58d-465c-ae41-6a52e9d76708|f4b04616-461e-46f9-b792-9a56ca58e05a</t>
+  </si>
+  <si>
+    <t>Esquema de rima observado</t>
+  </si>
+  <si>
+    <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B») (son 48 versos)</t>
+  </si>
+  <si>
+    <t>R|7116f6e7-c58d-465c-ae41-6a52e9d76708|eccfc812-2872-48f4-a7a3-6b8522f9f577</t>
+  </si>
+  <si>
+    <t>489–490</t>
+  </si>
+  <si>
+    <t>Pareado · De cualquier medida</t>
+  </si>
+  <si>
+    <t>Medida de los versos · estrofa 1 (vv. 489–490)</t>
+  </si>
+  <si>
+    <t>Indica 2, en orden y separadas por punto y coma, eligiendo entre: Tetrasílabo · Pentasílabo · Hexasílabo · Heptasílabo · Octosílabo · Endecasílabo · Dodecasílabo compuesto 6 + 6 · Dodecasílabo · Alejandrino</t>
+  </si>
+  <si>
+    <t>U|38f5bb60-4163-479d-81f6-19809152bb11|d87da020-d071-4ce2-b906-31f1529a4664|489</t>
+  </si>
+  <si>
+    <t>1041–1080</t>
+  </si>
+  <si>
+    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11») (son 40 versos)</t>
+  </si>
+  <si>
+    <t>R|a40c3f1f-7649-4901-9565-87f77f5186ec|f4b04616-461e-46f9-b792-9a56ca58e05a</t>
+  </si>
+  <si>
+    <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B») (son 40 versos)</t>
+  </si>
+  <si>
+    <t>R|a40c3f1f-7649-4901-9565-87f77f5186ec|eccfc812-2872-48f4-a7a3-6b8522f9f577</t>
+  </si>
+  <si>
+    <t>1081–1082</t>
+  </si>
+  <si>
+    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11») (son 2 versos)</t>
+  </si>
+  <si>
+    <t>R|0d790f28-3bdc-4a89-babe-3bc2030ff71d|f4b04616-461e-46f9-b792-9a56ca58e05a</t>
+  </si>
+  <si>
+    <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B») (son 2 versos)</t>
+  </si>
+  <si>
+    <t>R|0d790f28-3bdc-4a89-babe-3bc2030ff71d|eccfc812-2872-48f4-a7a3-6b8522f9f577</t>
+  </si>
+  <si>
+    <t>1481–1525</t>
+  </si>
+  <si>
+    <t>Canción petrarquista · Regular de 13 versos</t>
+  </si>
+  <si>
+    <t>Remate o envío · Medida de cada verso</t>
+  </si>
+  <si>
     <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11»)</t>
   </si>
   <si>
-    <t>R|7116f6e7-c58d-465c-ae41-6a52e9d76708|f4b04616-461e-46f9-b792-9a56ca58e05a</t>
-  </si>
-  <si>
-    <t>Esquema de rima observado</t>
+    <t>R|21da0a37-6600-40e7-bade-9a6bc3d226ea|428ea9b0-de26-4b97-b7bf-67f67f4492c1</t>
+  </si>
+  <si>
+    <t>Remate o envío · Esquema de rima observado</t>
   </si>
   <si>
     <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B»)</t>
   </si>
   <si>
-    <t>R|7116f6e7-c58d-465c-ae41-6a52e9d76708|eccfc812-2872-48f4-a7a3-6b8522f9f577</t>
-  </si>
-  <si>
-    <t>489–490</t>
-  </si>
-  <si>
-    <t>Pareado · De cualquier medida</t>
-  </si>
-  <si>
-    <t>Medida de los versos · estrofa 1 (vv. 489–490)</t>
-  </si>
-  <si>
-    <t>U|38f5bb60-4163-479d-81f6-19809152bb11|d87da020-d071-4ce2-b906-31f1529a4664|489</t>
-  </si>
-  <si>
-    <t>1041–1080</t>
-  </si>
-  <si>
-    <t>R|a40c3f1f-7649-4901-9565-87f77f5186ec|f4b04616-461e-46f9-b792-9a56ca58e05a</t>
-  </si>
-  <si>
-    <t>R|a40c3f1f-7649-4901-9565-87f77f5186ec|eccfc812-2872-48f4-a7a3-6b8522f9f577</t>
-  </si>
-  <si>
-    <t>1081–1082</t>
-  </si>
-  <si>
-    <t>R|0d790f28-3bdc-4a89-babe-3bc2030ff71d|f4b04616-461e-46f9-b792-9a56ca58e05a</t>
-  </si>
-  <si>
-    <t>R|0d790f28-3bdc-4a89-babe-3bc2030ff71d|eccfc812-2872-48f4-a7a3-6b8522f9f577</t>
-  </si>
-  <si>
-    <t>1481–1525</t>
-  </si>
-  <si>
-    <t>Canción petrarquista · Regular de 13 versos</t>
-  </si>
-  <si>
-    <t>Remate o envío · Medida de cada verso</t>
-  </si>
-  <si>
-    <t>R|21da0a37-6600-40e7-bade-9a6bc3d226ea|428ea9b0-de26-4b97-b7bf-67f67f4492c1</t>
-  </si>
-  <si>
-    <t>Remate o envío · Esquema de rima observado</t>
-  </si>
-  <si>
     <t>R|21da0a37-6600-40e7-bade-9a6bc3d226ea|76ad9ef5-a1d7-4669-a052-a80cbd0fb57d</t>
   </si>
   <si>
@@ -201,16 +222,28 @@
     <t>Versificación irregular · De arte menor</t>
   </si>
   <si>
+    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11») (son 37 versos)</t>
+  </si>
+  <si>
     <t>R|f5b40d8f-c193-4c42-b0b4-41265ff16e69|2532837f-c626-4b97-ab14-9d314ed4e22e</t>
   </si>
   <si>
+    <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B») (son 37 versos)</t>
+  </si>
+  <si>
     <t>R|f5b40d8f-c193-4c42-b0b4-41265ff16e69|a55e4b1c-206d-41c7-8f15-f5eeefceb2c0</t>
   </si>
   <si>
     <t>2334–2348</t>
   </si>
   <si>
+    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11») (son 15 versos)</t>
+  </si>
+  <si>
     <t>R|aad20dee-d37b-4cbd-8e1b-c5074588f3c0|f4b04616-461e-46f9-b792-9a56ca58e05a</t>
+  </si>
+  <si>
+    <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B») (son 15 versos)</t>
   </si>
   <si>
     <t>R|aad20dee-d37b-4cbd-8e1b-c5074588f3c0|eccfc812-2872-48f4-a7a3-6b8522f9f577</t>
@@ -1052,7 +1085,7 @@
         <v>30</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>30</v>
@@ -1064,7 +1097,7 @@
         <v>30</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1072,7 +1105,7 @@
         <v>26</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>28</v>
@@ -1084,7 +1117,7 @@
         <v>30</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>30</v>
@@ -1096,7 +1129,7 @@
         <v>30</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1104,7 +1137,7 @@
         <v>26</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>28</v>
@@ -1116,7 +1149,7 @@
         <v>30</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>30</v>
@@ -1128,7 +1161,7 @@
         <v>30</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1136,7 +1169,7 @@
         <v>26</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>28</v>
@@ -1148,7 +1181,7 @@
         <v>30</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>30</v>
@@ -1160,7 +1193,7 @@
         <v>30</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1168,7 +1201,7 @@
         <v>26</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>28</v>
@@ -1180,7 +1213,7 @@
         <v>30</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>30</v>
@@ -1192,7 +1225,7 @@
         <v>30</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1200,19 +1233,19 @@
         <v>26</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>30</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>30</v>
@@ -1224,7 +1257,7 @@
         <v>30</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1232,19 +1265,19 @@
         <v>26</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>30</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>30</v>
@@ -1256,7 +1289,7 @@
         <v>30</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1264,7 +1297,7 @@
         <v>26</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>28</v>
@@ -1276,7 +1309,7 @@
         <v>30</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>30</v>
@@ -1288,7 +1321,7 @@
         <v>30</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1296,7 +1329,7 @@
         <v>26</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>28</v>
@@ -1308,7 +1341,7 @@
         <v>30</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>30</v>
@@ -1320,7 +1353,7 @@
         <v>30</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1328,10 +1361,10 @@
         <v>26</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>29</v>
@@ -1340,7 +1373,7 @@
         <v>30</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>30</v>
@@ -1352,7 +1385,7 @@
         <v>30</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1360,10 +1393,10 @@
         <v>26</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>33</v>
@@ -1372,7 +1405,7 @@
         <v>30</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>30</v>
@@ -1384,7 +1417,7 @@
         <v>30</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1392,10 +1425,10 @@
         <v>26</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>29</v>
@@ -1404,7 +1437,7 @@
         <v>30</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>30</v>
@@ -1416,7 +1449,7 @@
         <v>30</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1424,10 +1457,10 @@
         <v>26</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>33</v>
@@ -1436,7 +1469,7 @@
         <v>30</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>30</v>
@@ -1448,7 +1481,7 @@
         <v>30</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1456,7 +1489,7 @@
         <v>26</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>28</v>
@@ -1468,7 +1501,7 @@
         <v>30</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>30</v>
@@ -1480,7 +1513,7 @@
         <v>30</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1488,7 +1521,7 @@
         <v>26</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>28</v>
@@ -1500,7 +1533,7 @@
         <v>30</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>30</v>
@@ -1512,7 +1545,7 @@
         <v>30</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1520,7 +1553,7 @@
         <v>26</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>28</v>
@@ -1532,7 +1565,7 @@
         <v>30</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>30</v>
@@ -1544,7 +1577,7 @@
         <v>30</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1552,7 +1585,7 @@
         <v>26</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>28</v>
@@ -1564,7 +1597,7 @@
         <v>30</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>30</v>
@@ -1576,7 +1609,7 @@
         <v>30</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1610,19 +1643,19 @@
         <v>18</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>22</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>24</v>
@@ -1633,19 +1666,19 @@
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>30</v>
@@ -1657,7 +1690,7 @@
         <v>30</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1668,13 +1701,13 @@
         <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>30</v>
@@ -1686,24 +1719,24 @@
         <v>30</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>30</v>
@@ -1715,24 +1748,24 @@
         <v>30</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="C5" s="3" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>30</v>
@@ -1744,24 +1777,24 @@
         <v>30</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="E6" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>30</v>
@@ -1773,24 +1806,24 @@
         <v>30</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>30</v>
@@ -1802,24 +1835,24 @@
         <v>30</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>30</v>
@@ -1831,7 +1864,7 @@
         <v>30</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1871,22 +1904,22 @@
         <v>17</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>24</v>
@@ -1922,37 +1955,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>18</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>20</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1960,34 +1993,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C2" s="3">
         <v>440</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2001,28 +2034,28 @@
         <v>48</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2036,28 +2069,28 @@
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2065,34 +2098,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="C5" s="3">
         <v>550</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2100,34 +2133,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6" s="3">
         <v>40</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2135,34 +2168,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C7" s="3">
         <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2170,34 +2203,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="C8" s="3">
         <v>398</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2205,34 +2238,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C9" s="3">
         <v>45</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2240,34 +2273,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C10" s="3">
         <v>350</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2275,34 +2308,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C11" s="3">
         <v>40</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2310,34 +2343,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C12" s="3">
         <v>2</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2345,34 +2378,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="C13" s="3">
         <v>338</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2380,34 +2413,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C14" s="3">
         <v>37</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2415,34 +2448,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C15" s="3">
         <v>41</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2450,34 +2483,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="C16" s="3">
         <v>15</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2485,34 +2518,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C17" s="3">
         <v>2</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/elisa-dido.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/elisa-dido.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="156">
   <si>
     <t>Migración métrica · Elisa Dido</t>
   </si>
@@ -60,12 +60,72 @@
     <t>lista</t>
   </si>
   <si>
+    <t>a</t>
+  </si>
+  <si>
     <t>Es correcto</t>
   </si>
   <si>
+    <t>a-a</t>
+  </si>
+  <si>
     <t>No es así (lo corrijo al lado)</t>
   </si>
   <si>
+    <t>a-e</t>
+  </si>
+  <si>
+    <t>a-o</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>e-a</t>
+  </si>
+  <si>
+    <t>e-e</t>
+  </si>
+  <si>
+    <t>e-o</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>i-a</t>
+  </si>
+  <si>
+    <t>i-e</t>
+  </si>
+  <si>
+    <t>i-o</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>o-a</t>
+  </si>
+  <si>
+    <t>o-e</t>
+  </si>
+  <si>
+    <t>o-o</t>
+  </si>
+  <si>
+    <t>u</t>
+  </si>
+  <si>
+    <t>u-a</t>
+  </si>
+  <si>
+    <t>u-e</t>
+  </si>
+  <si>
+    <t>u-o</t>
+  </si>
+  <si>
     <t>Tipo</t>
   </si>
   <si>
@@ -129,16 +189,16 @@
     <t>489–490</t>
   </si>
   <si>
-    <t>Pareado · De cualquier medida</t>
-  </si>
-  <si>
-    <t>Medida de los versos · estrofa 1 (vv. 489–490)</t>
-  </si>
-  <si>
-    <t>Indica 2, en orden y separadas por punto y coma, eligiendo entre: Tetrasílabo · Pentasílabo · Hexasílabo · Heptasílabo · Octosílabo · Endecasílabo · Dodecasílabo compuesto 6 + 6 · Dodecasílabo · Alejandrino</t>
-  </si>
-  <si>
-    <t>U|38f5bb60-4163-479d-81f6-19809152bb11|d87da020-d071-4ce2-b906-31f1529a4664|489</t>
+    <t>Pareado · Isométrico</t>
+  </si>
+  <si>
+    <t>Vocales de la asonancia</t>
+  </si>
+  <si>
+    <t>Elige en el desplegable</t>
+  </si>
+  <si>
+    <t>R|38f5bb60-4163-479d-81f6-19809152bb11|da2e8262-3dbf-43d4-ba62-f492fa06dc8b</t>
   </si>
   <si>
     <t>1041–1080</t>
@@ -180,7 +240,7 @@
     <t>Remate o envío · Medida de cada verso</t>
   </si>
   <si>
-    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11»)</t>
+    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11»). Solo si este pasaje lleva remate o envío; si no, déjalo en blanco</t>
   </si>
   <si>
     <t>R|21da0a37-6600-40e7-bade-9a6bc3d226ea|428ea9b0-de26-4b97-b7bf-67f67f4492c1</t>
@@ -189,7 +249,7 @@
     <t>Remate o envío · Esquema de rima observado</t>
   </si>
   <si>
-    <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B»)</t>
+    <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B»). Solo si este pasaje lleva remate o envío; si no, déjalo en blanco</t>
   </si>
   <si>
     <t>R|21da0a37-6600-40e7-bade-9a6bc3d226ea|76ad9ef5-a1d7-4669-a052-a80cbd0fb57d</t>
@@ -288,10 +348,7 @@
     <t>C|673fbb2c-877d-44a0-a3ea-f80fb8b99905</t>
   </si>
   <si>
-    <t>Esquema de rima</t>
-  </si>
-  <si>
-    <t>aa · Consonante</t>
+    <t>Esquema de rima: aa · Consonante; Medida de los versos: Endecasílabo</t>
   </si>
   <si>
     <t>pareado_endecasilabo</t>
@@ -399,13 +456,13 @@
     <t>Pareado</t>
   </si>
   <si>
-    <t>De cualquier medida</t>
-  </si>
-  <si>
-    <t>Falta: Medida de los versos</t>
-  </si>
-  <si>
-    <t>1 derivada</t>
+    <t>Isométrico</t>
+  </si>
+  <si>
+    <t>Falta: Vocales de la asonancia</t>
+  </si>
+  <si>
+    <t>2 derivadas</t>
   </si>
   <si>
     <t>cancion_regular_abCabCcdeeDfF</t>
@@ -415,9 +472,6 @@
   </si>
   <si>
     <t>Regular de 13 versos</t>
-  </si>
-  <si>
-    <t>Falta: Remate o envío · Medida de cada verso, Remate o envío · Esquema de rima observado</t>
   </si>
   <si>
     <t>irregular_arte_mayor</t>
@@ -929,25 +983,124 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="1" max="2" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -974,646 +1127,651 @@
   <sheetData>
     <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G4">
+      <formula1>Listas!$A$2:$A$21</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1637,241 +1795,241 @@
   <sheetData>
     <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="F2:F8">
-      <formula1>Listas!$A$2:$A$3</formula1>
+      <formula1>Listas!$B$2:$B$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1898,34 +2056,34 @@
   <sheetData>
     <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1955,37 +2113,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1993,34 +2151,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="C2" s="3">
         <v>440</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2028,34 +2186,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C3" s="3">
         <v>48</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2063,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2098,34 +2256,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="C5" s="3">
         <v>550</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2133,34 +2291,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="C6" s="3">
         <v>40</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2168,34 +2326,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C7" s="3">
         <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2203,34 +2361,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="C8" s="3">
         <v>398</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2238,34 +2396,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C9" s="3">
         <v>45</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>133</v>
+        <v>13</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2273,34 +2431,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="C10" s="3">
         <v>350</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2308,34 +2466,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="C11" s="3">
         <v>40</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2343,34 +2501,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="C12" s="3">
         <v>2</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2378,34 +2536,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C13" s="3">
         <v>338</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2413,34 +2571,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="C14" s="3">
         <v>37</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2448,34 +2606,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C15" s="3">
         <v>41</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2483,34 +2641,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C16" s="3">
         <v>15</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2518,34 +2676,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="C17" s="3">
         <v>2</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>124</v>
+        <v>143</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/elisa-dido.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/elisa-dido.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="132">
   <si>
     <t>Migración métrica · Elisa Dido</t>
   </si>
@@ -60,72 +60,12 @@
     <t>lista</t>
   </si>
   <si>
-    <t>a</t>
-  </si>
-  <si>
     <t>Es correcto</t>
   </si>
   <si>
-    <t>a-a</t>
-  </si>
-  <si>
     <t>No es así (lo corrijo al lado)</t>
   </si>
   <si>
-    <t>a-e</t>
-  </si>
-  <si>
-    <t>a-o</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>e-a</t>
-  </si>
-  <si>
-    <t>e-e</t>
-  </si>
-  <si>
-    <t>e-o</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>i-a</t>
-  </si>
-  <si>
-    <t>i-e</t>
-  </si>
-  <si>
-    <t>i-o</t>
-  </si>
-  <si>
-    <t>o</t>
-  </si>
-  <si>
-    <t>o-a</t>
-  </si>
-  <si>
-    <t>o-e</t>
-  </si>
-  <si>
-    <t>o-o</t>
-  </si>
-  <si>
-    <t>u</t>
-  </si>
-  <si>
-    <t>u-a</t>
-  </si>
-  <si>
-    <t>u-e</t>
-  </si>
-  <si>
-    <t>u-o</t>
-  </si>
-  <si>
     <t>Tipo</t>
   </si>
   <si>
@@ -186,168 +126,159 @@
     <t>R|7116f6e7-c58d-465c-ae41-6a52e9d76708|eccfc812-2872-48f4-a7a3-6b8522f9f577</t>
   </si>
   <si>
+    <t>1041–1080</t>
+  </si>
+  <si>
+    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11») (son 40 versos)</t>
+  </si>
+  <si>
+    <t>R|a40c3f1f-7649-4901-9565-87f77f5186ec|f4b04616-461e-46f9-b792-9a56ca58e05a</t>
+  </si>
+  <si>
+    <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B») (son 40 versos)</t>
+  </si>
+  <si>
+    <t>R|a40c3f1f-7649-4901-9565-87f77f5186ec|eccfc812-2872-48f4-a7a3-6b8522f9f577</t>
+  </si>
+  <si>
+    <t>1081–1082</t>
+  </si>
+  <si>
+    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11») (son 2 versos)</t>
+  </si>
+  <si>
+    <t>R|0d790f28-3bdc-4a89-babe-3bc2030ff71d|f4b04616-461e-46f9-b792-9a56ca58e05a</t>
+  </si>
+  <si>
+    <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B») (son 2 versos)</t>
+  </si>
+  <si>
+    <t>R|0d790f28-3bdc-4a89-babe-3bc2030ff71d|eccfc812-2872-48f4-a7a3-6b8522f9f577</t>
+  </si>
+  <si>
+    <t>1481–1525</t>
+  </si>
+  <si>
+    <t>Canción petrarquista · Regular de 13 versos</t>
+  </si>
+  <si>
+    <t>Remate o envío · Medida de cada verso</t>
+  </si>
+  <si>
+    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11»). Solo si este pasaje lleva remate o envío; si no, déjalo en blanco</t>
+  </si>
+  <si>
+    <t>R|21da0a37-6600-40e7-bade-9a6bc3d226ea|428ea9b0-de26-4b97-b7bf-67f67f4492c1</t>
+  </si>
+  <si>
+    <t>Remate o envío · Esquema de rima observado</t>
+  </si>
+  <si>
+    <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B»). Solo si este pasaje lleva remate o envío; si no, déjalo en blanco</t>
+  </si>
+  <si>
+    <t>R|21da0a37-6600-40e7-bade-9a6bc3d226ea|76ad9ef5-a1d7-4669-a052-a80cbd0fb57d</t>
+  </si>
+  <si>
+    <t>1876–1915</t>
+  </si>
+  <si>
+    <t>R|4c2e929e-2ee1-4620-8542-a7b3c8b3cb44|f4b04616-461e-46f9-b792-9a56ca58e05a</t>
+  </si>
+  <si>
+    <t>R|4c2e929e-2ee1-4620-8542-a7b3c8b3cb44|eccfc812-2872-48f4-a7a3-6b8522f9f577</t>
+  </si>
+  <si>
+    <t>1916–1917</t>
+  </si>
+  <si>
+    <t>Versificación irregular · De arte mayor</t>
+  </si>
+  <si>
+    <t>R|b1053bb9-699f-447e-9d49-617681517240|fc2daf7e-d96f-425b-bffb-08ded4bb661b</t>
+  </si>
+  <si>
+    <t>R|b1053bb9-699f-447e-9d49-617681517240|2ccf2c10-53c3-4efc-99f5-4856b9565b35</t>
+  </si>
+  <si>
+    <t>2256–2292</t>
+  </si>
+  <si>
+    <t>Versificación irregular · De arte menor</t>
+  </si>
+  <si>
+    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11») (son 37 versos)</t>
+  </si>
+  <si>
+    <t>R|f5b40d8f-c193-4c42-b0b4-41265ff16e69|2532837f-c626-4b97-ab14-9d314ed4e22e</t>
+  </si>
+  <si>
+    <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B») (son 37 versos)</t>
+  </si>
+  <si>
+    <t>R|f5b40d8f-c193-4c42-b0b4-41265ff16e69|a55e4b1c-206d-41c7-8f15-f5eeefceb2c0</t>
+  </si>
+  <si>
+    <t>2334–2348</t>
+  </si>
+  <si>
+    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11») (son 15 versos)</t>
+  </si>
+  <si>
+    <t>R|aad20dee-d37b-4cbd-8e1b-c5074588f3c0|f4b04616-461e-46f9-b792-9a56ca58e05a</t>
+  </si>
+  <si>
+    <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B») (son 15 versos)</t>
+  </si>
+  <si>
+    <t>R|aad20dee-d37b-4cbd-8e1b-c5074588f3c0|eccfc812-2872-48f4-a7a3-6b8522f9f577</t>
+  </si>
+  <si>
+    <t>2349–2350</t>
+  </si>
+  <si>
+    <t>R|1259a26d-4246-49d2-830d-4e581912d2d6|f4b04616-461e-46f9-b792-9a56ca58e05a</t>
+  </si>
+  <si>
+    <t>R|1259a26d-4246-49d2-830d-4e581912d2d6|eccfc812-2872-48f4-a7a3-6b8522f9f577</t>
+  </si>
+  <si>
+    <t>Pregunta</t>
+  </si>
+  <si>
+    <t>Vocabulario anterior</t>
+  </si>
+  <si>
+    <t>¿Correcto?</t>
+  </si>
+  <si>
+    <t>Corrección</t>
+  </si>
+  <si>
+    <t>1–440</t>
+  </si>
+  <si>
+    <t>Endecasílabo suelto · Endecasílabo</t>
+  </si>
+  <si>
+    <t>Varias respuestas</t>
+  </si>
+  <si>
+    <t>Densidad de rima: Ninguna; Dístico final: sí; Organización en pareados: Ninguna</t>
+  </si>
+  <si>
+    <t>endecasilabo_suelto_puro</t>
+  </si>
+  <si>
+    <t>C|673fbb2c-877d-44a0-a3ea-f80fb8b99905</t>
+  </si>
+  <si>
     <t>489–490</t>
   </si>
   <si>
     <t>Pareado · Isométrico</t>
   </si>
   <si>
-    <t>Vocales de la asonancia</t>
-  </si>
-  <si>
-    <t>Elige en el desplegable</t>
-  </si>
-  <si>
-    <t>R|38f5bb60-4163-479d-81f6-19809152bb11|da2e8262-3dbf-43d4-ba62-f492fa06dc8b</t>
-  </si>
-  <si>
-    <t>1041–1080</t>
-  </si>
-  <si>
-    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11») (son 40 versos)</t>
-  </si>
-  <si>
-    <t>R|a40c3f1f-7649-4901-9565-87f77f5186ec|f4b04616-461e-46f9-b792-9a56ca58e05a</t>
-  </si>
-  <si>
-    <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B») (son 40 versos)</t>
-  </si>
-  <si>
-    <t>R|a40c3f1f-7649-4901-9565-87f77f5186ec|eccfc812-2872-48f4-a7a3-6b8522f9f577</t>
-  </si>
-  <si>
-    <t>1081–1082</t>
-  </si>
-  <si>
-    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11») (son 2 versos)</t>
-  </si>
-  <si>
-    <t>R|0d790f28-3bdc-4a89-babe-3bc2030ff71d|f4b04616-461e-46f9-b792-9a56ca58e05a</t>
-  </si>
-  <si>
-    <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B») (son 2 versos)</t>
-  </si>
-  <si>
-    <t>R|0d790f28-3bdc-4a89-babe-3bc2030ff71d|eccfc812-2872-48f4-a7a3-6b8522f9f577</t>
-  </si>
-  <si>
-    <t>1481–1525</t>
-  </si>
-  <si>
-    <t>Canción petrarquista · Regular de 13 versos</t>
-  </si>
-  <si>
-    <t>Remate o envío · Medida de cada verso</t>
-  </si>
-  <si>
-    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11»). Solo si este pasaje lleva remate o envío; si no, déjalo en blanco</t>
-  </si>
-  <si>
-    <t>R|21da0a37-6600-40e7-bade-9a6bc3d226ea|428ea9b0-de26-4b97-b7bf-67f67f4492c1</t>
-  </si>
-  <si>
-    <t>Remate o envío · Esquema de rima observado</t>
-  </si>
-  <si>
-    <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B»). Solo si este pasaje lleva remate o envío; si no, déjalo en blanco</t>
-  </si>
-  <si>
-    <t>R|21da0a37-6600-40e7-bade-9a6bc3d226ea|76ad9ef5-a1d7-4669-a052-a80cbd0fb57d</t>
-  </si>
-  <si>
-    <t>1876–1915</t>
-  </si>
-  <si>
-    <t>R|4c2e929e-2ee1-4620-8542-a7b3c8b3cb44|f4b04616-461e-46f9-b792-9a56ca58e05a</t>
-  </si>
-  <si>
-    <t>R|4c2e929e-2ee1-4620-8542-a7b3c8b3cb44|eccfc812-2872-48f4-a7a3-6b8522f9f577</t>
-  </si>
-  <si>
-    <t>1916–1917</t>
-  </si>
-  <si>
-    <t>Versificación irregular · De arte mayor</t>
-  </si>
-  <si>
-    <t>R|b1053bb9-699f-447e-9d49-617681517240|fc2daf7e-d96f-425b-bffb-08ded4bb661b</t>
-  </si>
-  <si>
-    <t>R|b1053bb9-699f-447e-9d49-617681517240|2ccf2c10-53c3-4efc-99f5-4856b9565b35</t>
-  </si>
-  <si>
-    <t>2256–2292</t>
-  </si>
-  <si>
-    <t>Versificación irregular · De arte menor</t>
-  </si>
-  <si>
-    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11») (son 37 versos)</t>
-  </si>
-  <si>
-    <t>R|f5b40d8f-c193-4c42-b0b4-41265ff16e69|2532837f-c626-4b97-ab14-9d314ed4e22e</t>
-  </si>
-  <si>
-    <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B») (son 37 versos)</t>
-  </si>
-  <si>
-    <t>R|f5b40d8f-c193-4c42-b0b4-41265ff16e69|a55e4b1c-206d-41c7-8f15-f5eeefceb2c0</t>
-  </si>
-  <si>
-    <t>2334–2348</t>
-  </si>
-  <si>
-    <t>Escribe el número de sílabas de cada verso, en orden y separados por espacios («7 11 7 7 11») (son 15 versos)</t>
-  </si>
-  <si>
-    <t>R|aad20dee-d37b-4cbd-8e1b-c5074588f3c0|f4b04616-461e-46f9-b792-9a56ca58e05a</t>
-  </si>
-  <si>
-    <t>Escribe una letra por verso, en mayúscula si es de arte mayor y un guion si el verso queda suelto («aBab-B») (son 15 versos)</t>
-  </si>
-  <si>
-    <t>R|aad20dee-d37b-4cbd-8e1b-c5074588f3c0|eccfc812-2872-48f4-a7a3-6b8522f9f577</t>
-  </si>
-  <si>
-    <t>2349–2350</t>
-  </si>
-  <si>
-    <t>R|1259a26d-4246-49d2-830d-4e581912d2d6|f4b04616-461e-46f9-b792-9a56ca58e05a</t>
-  </si>
-  <si>
-    <t>R|1259a26d-4246-49d2-830d-4e581912d2d6|eccfc812-2872-48f4-a7a3-6b8522f9f577</t>
-  </si>
-  <si>
-    <t>Pregunta</t>
-  </si>
-  <si>
-    <t>Vocabulario anterior</t>
-  </si>
-  <si>
-    <t>¿Correcto?</t>
-  </si>
-  <si>
-    <t>Corrección</t>
-  </si>
-  <si>
-    <t>1–440</t>
-  </si>
-  <si>
-    <t>Endecasílabo suelto · Endecasílabo</t>
-  </si>
-  <si>
-    <t>Varias respuestas</t>
-  </si>
-  <si>
-    <t>Densidad de rima: Ninguna; Dístico final: sí; Organización en pareados: Ninguna</t>
-  </si>
-  <si>
-    <t>endecasilabo_suelto_puro</t>
-  </si>
-  <si>
-    <t>C|673fbb2c-877d-44a0-a3ea-f80fb8b99905</t>
-  </si>
-  <si>
     <t>Esquema de rima: aa · Consonante; Medida de los versos: Endecasílabo</t>
   </si>
   <si>
@@ -457,9 +388,6 @@
   </si>
   <si>
     <t>Isométrico</t>
-  </si>
-  <si>
-    <t>Falta: Vocales de la asonancia</t>
   </si>
   <si>
     <t>2 derivadas</t>
@@ -983,124 +911,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="40" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1111,7 +940,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
@@ -1127,651 +956,614 @@
   <sheetData>
     <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>68</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="C8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="E8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8" s="7" t="s">
         <v>50</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="C9" s="3" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="G4">
-      <formula1>Listas!$A$2:$A$21</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1795,241 +1587,241 @@
   <sheetData>
     <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Elige una opción" error="Elige una de las opciones del desplegable." sqref="F2:F8">
-      <formula1>Listas!$B$2:$B$3</formula1>
+      <formula1>Listas!$A$2:$A$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2056,34 +1848,34 @@
   <sheetData>
     <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2113,37 +1905,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2151,34 +1943,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="C2" s="3">
         <v>440</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2186,34 +1978,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3">
         <v>48</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2221,34 +2013,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="C4" s="3">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>147</v>
+        <v>13</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2256,34 +2048,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="C5" s="3">
         <v>550</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2291,34 +2083,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="C6" s="3">
         <v>40</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2326,34 +2118,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="C7" s="3">
         <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2361,34 +2153,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="C8" s="3">
         <v>398</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2396,34 +2188,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="C9" s="3">
         <v>45</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2431,34 +2223,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="C10" s="3">
         <v>350</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2466,34 +2258,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="C11" s="3">
         <v>40</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2501,34 +2293,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="C12" s="3">
         <v>2</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2536,34 +2328,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="C13" s="3">
         <v>338</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2571,34 +2363,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="C14" s="3">
         <v>37</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2606,34 +2398,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="C15" s="3">
         <v>41</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2641,34 +2433,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="C16" s="3">
         <v>15</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2676,34 +2468,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C17" s="3">
         <v>2</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/docs/dominio-metrico/migracion/cuestionarios/elisa-dido.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/elisa-dido.xlsx
@@ -27,7 +27,7 @@
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
   </si>
   <si>
-    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta. Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato. Las preguntas que se refieren a cada estrofa aparecen de dos maneras: si son pocas estrofas, hay una fila por estrofa; si son muchas, hay una sola fila cuya respuesta vale para todas, y las estrofas que se aparten de ella se anotan en «Excepciones / detalle» indicando los versos y la respuesta, por ejemplo «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle» como «versos: esquema», por ejemplo «191-194: abab; 203-206: abab». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato.</t>
   </si>
   <si>
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
@@ -54,7 +54,7 @@
     <t>Esquema de rima: una letra por verso, en mayúscula si el verso es de arte mayor y un guion si queda suelto. Por ejemplo, «aBab-B».</t>
   </si>
   <si>
-    <t>Excepciones: los versos de la estrofa y la respuesta que le corresponde, separando cada estrofa con punto y coma. Por ejemplo, «191–194: Cruzada · abab; 203–206: Cruzada · abab».</t>
+    <t>Excepciones: los versos de la estrofa y su esquema, separados por dos puntos, y cada estrofa de la siguiente con punto y coma. Por ejemplo, «191-194: abab; 203-206: abab». El esquema se escribe como arriba: una letra por verso, en mayúscula si el verso es de arte mayor.</t>
   </si>
   <si>
     <t>lista</t>

--- a/docs/dominio-metrico/migracion/cuestionarios/elisa-dido.xlsx
+++ b/docs/dominio-metrico/migracion/cuestionarios/elisa-dido.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="127">
   <si>
     <t>Migración métrica · Elisa Dido</t>
   </si>
@@ -27,7 +27,7 @@
     <t>El Excel tiene cinco pestañas. En tres de ellas hay que escribir —Responder, Confirmar y Desviaciones— y las otras dos son de consulta: Secuencias, con todo lo que tiene anotado tu obra, e Instrucciones, donde estás ahora. Solo hace falta escribir en las columnas de fondo amarillo, que son «Respuesta», «Excepciones / detalle» y «Comentario». El resto de columnas las genera el programa y las necesita tal cual para poder leer las respuestas, así que conviene no tocarlas.</t>
   </si>
   <si>
-    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle» como «versos: esquema», por ejemplo «191-194: abab; 203-206: abab». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» explica el formato.</t>
+    <t>En Responder están las preguntas que no he podido contestar con lo que ya tenías anotado. Cada fila corresponde a un pasaje y a una pregunta, también cuando la pregunta es de cada estrofa: se contesta una vez y la respuesta vale para todas, y las estrofas que se aparten se anotan en «Excepciones / detalle». Cuando la celda tiene desplegable, basta con elegir; cuando no, la columna «Cómo contestar» dice el formato y da un ejemplo.</t>
   </si>
   <si>
     <t>Las filas marcadas como Decidir señalan pasajes cuyo número de versos no encaja con la forma que tienen asignada. En ellas hay que elegir en el desplegable qué ocurre y explicarlo al lado. Si se trata de una laguna que no se contó, indica en qué verso está y cuántos versos faltan, porque los añadiré a la numeración y todo lo que viene después se desplazará. Si lo que falla es el rango, escribe el rango correcto.</t>
@@ -40,21 +40,6 @@
   </si>
   <si>
     <t>Si algo no está claro o no sabes cómo contestarlo, pregúntamelo antes de dejarlo a medias. Una vez hecha la migración podrás ver cada secuencia de tu obra con el editor nuevo en el dashboard y comprobar allí que la migración no dejó ningún hueco.</t>
-  </si>
-  <si>
-    <t>Cuando no hay desplegable, los formatos son estos:</t>
-  </si>
-  <si>
-    <t>Medidas: el número de sílabas de cada verso, en orden y separados por espacios. Por ejemplo, «7 11 7 7 11 7 11 11».</t>
-  </si>
-  <si>
-    <t>Posiciones: en qué versos de la estrofa cae el quebrado y cuántas sílabas tiene cada uno, separados por comas. Por ejemplo, «3: 4, 8: 5» quiere decir que el verso 3 tiene cuatro sílabas y el 8 tiene cinco.</t>
-  </si>
-  <si>
-    <t>Esquema de rima: una letra por verso, en mayúscula si el verso es de arte mayor y un guion si queda suelto. Por ejemplo, «aBab-B».</t>
-  </si>
-  <si>
-    <t>Excepciones: los versos de la estrofa y su esquema, separados por dos puntos, y cada estrofa de la siguiente con punto y coma. Por ejemplo, «191-194: abab; 203-206: abab». El esquema se escribe como arriba: una letra por verso, en mayúscula si el verso es de arte mayor.</t>
   </si>
   <si>
     <t>lista</t>
@@ -476,14 +461,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -832,7 +816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -876,31 +860,6 @@
     <row r="9" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -919,17 +878,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -954,612 +913,612 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="G2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="E3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>38</v>
+        <v>32</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="E5" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>40</v>
+        <v>34</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>43</v>
+        <v>37</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="E7" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>53</v>
+      <c r="G9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>55</v>
+        <v>32</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="E11" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>56</v>
+        <v>34</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>59</v>
+        <v>37</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>60</v>
+        <v>39</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>69</v>
+        <v>63</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="E17" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>71</v>
+        <v>65</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>73</v>
+        <v>37</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="E19" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>74</v>
+        <v>39</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1585,236 +1544,236 @@
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>25</v>
+      <c r="E1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>89</v>
+        <v>83</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>91</v>
+        <v>78</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>93</v>
+        <v>78</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>95</v>
+        <v>78</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>97</v>
+        <v>78</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>99</v>
+        <v>78</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1846,36 +1805,36 @@
     <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>25</v>
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1903,39 +1862,39 @@
     <col min="11" max="11" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="J1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1943,34 +1902,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C2" s="3">
         <v>440</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1978,34 +1937,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3">
         <v>48</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2013,34 +1972,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C4" s="3">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2048,34 +2007,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C5" s="3">
         <v>550</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2083,34 +2042,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C6" s="3">
         <v>40</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2118,34 +2077,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C7" s="3">
         <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2153,34 +2112,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C8" s="3">
         <v>398</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2188,34 +2147,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C9" s="3">
         <v>45</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2223,34 +2182,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3">
         <v>350</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2258,34 +2217,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C11" s="3">
         <v>40</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2293,34 +2252,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C12" s="3">
         <v>2</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2328,34 +2287,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C13" s="3">
         <v>338</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2363,34 +2322,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C14" s="3">
         <v>37</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2398,34 +2357,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C15" s="3">
         <v>41</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2433,34 +2392,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C16" s="3">
         <v>15</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2468,34 +2427,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C17" s="3">
         <v>2</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
